--- a/BADesign/Excel/Quest.xlsx
+++ b/BADesign/Excel/Quest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.293.56114"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="580" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Quest" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Client</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Quest에서 소환할 몬스터 Tid, SpawnCount</t>
+  </si>
+  <si>
+    <t>Boss1Stage</t>
   </si>
 </sst>
 </file>
@@ -94,7 +97,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -212,11 +215,6 @@
     <font>
       <sz val="10.0"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -449,25 +447,21 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -482,7 +476,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -497,7 +490,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -512,13 +504,11 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <top style="thin">
@@ -527,7 +517,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1034,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="5" max="7" width="11.13000011" customWidth="1" outlineLevel="0"/>
@@ -1105,6 +1094,27 @@
       </c>
       <c r="G3" s="5">
         <v>501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5">
+        <v>2001</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>20003</v>
+      </c>
+      <c r="F4" s="5">
+        <v>20004</v>
+      </c>
+      <c r="G4" s="5">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
